--- a/output/pdf_financials_xlsx/ANRG.xlsx
+++ b/output/pdf_financials_xlsx/ANRG.xlsx
@@ -1289,10 +1289,10 @@
         <v>79.31699999999999</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>55.378</v>
+        <v>79.31699999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>22.113</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>30.22</v>
@@ -1339,10 +1339,10 @@
         <v>79.31699999999999</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>55.378</v>
+        <v>79.31699999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>22.113</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>30.22</v>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">

--- a/output/pdf_financials_xlsx/ANRG.xlsx
+++ b/output/pdf_financials_xlsx/ANRG.xlsx
@@ -15094,7 +15094,11 @@
           <t>Income tax recovery (expense) 15</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
